--- a/data/industry/Automobile/MUVVI.xlsx
+++ b/data/industry/Automobile/MUVVI.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10118"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\krm\PycharmProjects\AlternativeData\data\industry\Automobile\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/tommy/Desktop/Pycharm/FinancialData/data/industry/Automobile/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B681BFE8-BB44-4698-B508-2037B06A11CF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DBD69D2F-B05B-3543-A45B-3827A8114E3E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="22160" yWindow="600" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="MANHEIM" sheetId="1" r:id="rId1"/>
@@ -37,12 +37,6 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="15">
   <si>
-    <t>SA EV</t>
-  </si>
-  <si>
-    <t>SA Non-EV</t>
-  </si>
-  <si>
     <t>source</t>
   </si>
   <si>
@@ -67,26 +61,33 @@
     <t>Time Zone</t>
   </si>
   <si>
-    <t>Manheim Index</t>
+    <t>MANHEIM</t>
   </si>
   <si>
-    <t>Manheim Index NSA</t>
+    <t>MANHEIMSA</t>
   </si>
   <si>
-    <t>Manheim Index SA</t>
+    <t>MANHEIMNSA</t>
   </si>
   <si>
-    <t>Non-EV Index</t>
+    <t>EVSA</t>
   </si>
   <si>
-    <t>EV Index</t>
+    <t>NONEVSA</t>
+  </si>
+  <si>
+    <t>EV</t>
+  </si>
+  <si>
+    <t>NONEV</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="7">
+  <numFmts count="8">
+    <numFmt numFmtId="41" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;_);_(@_)"/>
     <numFmt numFmtId="43" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
     <numFmt numFmtId="164" formatCode="0.0"/>
     <numFmt numFmtId="165" formatCode="[$-409]mmm\-yy;@"/>
@@ -157,7 +158,7 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="7">
+  <cellStyleXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
@@ -165,8 +166,9 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="43" fontId="1" fillId="0" borderId="0" xfId="5" applyFont="1"/>
     <xf numFmtId="168" fontId="1" fillId="0" borderId="0" xfId="5" applyNumberFormat="1" applyFont="1"/>
@@ -207,15 +209,17 @@
     <xf numFmtId="3" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="6"/>
     <xf numFmtId="14" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" xfId="7" applyFont="1"/>
   </cellXfs>
-  <cellStyles count="7">
+  <cellStyles count="8">
+    <cellStyle name="Comma" xfId="5" builtinId="3"/>
+    <cellStyle name="Comma [0]" xfId="7" builtinId="6"/>
+    <cellStyle name="Hyperlink" xfId="6" builtinId="8"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Normal 2" xfId="2" xr:uid="{90624D1E-5ED3-4424-9C13-3E2409B87A6C}"/>
     <cellStyle name="Normal 3" xfId="4" xr:uid="{177934AF-8E12-448A-89BD-47D02E7FAFB3}"/>
+    <cellStyle name="Percent" xfId="1" builtinId="5"/>
     <cellStyle name="Percent 2" xfId="3" xr:uid="{31DF82BF-D42C-4ED6-A369-0AB68ABDFE12}"/>
-    <cellStyle name="백분율" xfId="1" builtinId="5"/>
-    <cellStyle name="쉼표" xfId="5" builtinId="3"/>
-    <cellStyle name="표준" xfId="0" builtinId="0"/>
-    <cellStyle name="하이퍼링크" xfId="6" builtinId="8"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -518,60 +522,59 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:O361"/>
-  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="12.109375" style="9" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="13.109375" style="9" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.1640625" style="9" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.1640625" style="9" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="12" style="18" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="10.77734375" style="11" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.5546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="17.33203125" style="2" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="18.77734375" style="2" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="7.77734375" style="7" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="11.5546875" style="19" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="9.88671875" style="7" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.33203125" style="7" bestFit="1" customWidth="1"/>
-    <col min="12" max="13" width="8.77734375" style="7"/>
-    <col min="14" max="14" width="20.44140625" style="7" bestFit="1" customWidth="1"/>
-    <col min="15" max="16384" width="8.77734375" style="7"/>
+    <col min="4" max="4" width="10.83203125" style="11" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="9.83203125" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="11.6640625" style="2" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="12.83203125" style="2" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="7.6640625" style="7" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="9.33203125" style="19" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="7.6640625" style="7" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="8.83203125" style="7"/>
+    <col min="14" max="14" width="20.5" style="7" bestFit="1" customWidth="1"/>
+    <col min="15" max="16384" width="8.83203125" style="7"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" s="8" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:14" s="8" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A1" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="B1" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="C1" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="B1" s="5" t="s">
+      <c r="D1" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="C1" s="6" t="s">
+      <c r="E1" s="22" t="s">
         <v>8</v>
       </c>
-      <c r="D1" s="4" t="s">
+      <c r="F1" s="22" t="s">
         <v>9</v>
       </c>
-      <c r="E1" s="7" t="s">
+      <c r="G1" s="22" t="s">
         <v>10</v>
       </c>
-      <c r="F1" s="7" t="s">
+      <c r="H1" s="22" t="s">
+        <v>11</v>
+      </c>
+      <c r="I1" s="22" t="s">
         <v>12</v>
       </c>
-      <c r="G1" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="H1" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="I1" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="J1" s="1" t="s">
+      <c r="J1" s="22" t="s">
+        <v>13</v>
+      </c>
+      <c r="K1" s="22" t="s">
         <v>14</v>
       </c>
-      <c r="K1" s="1" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.3">
+    </row>
+    <row r="2" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A2" s="9">
         <v>35431</v>
       </c>
@@ -616,7 +619,7 @@
       <c r="L2" s="12"/>
       <c r="N2" s="21"/>
     </row>
-    <row r="3" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A3" s="9">
         <v>35462</v>
       </c>
@@ -661,7 +664,7 @@
       <c r="L3" s="12"/>
       <c r="N3" s="21"/>
     </row>
-    <row r="4" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A4" s="9">
         <v>35490</v>
       </c>
@@ -691,7 +694,7 @@
       <c r="L4" s="12"/>
       <c r="N4" s="21"/>
     </row>
-    <row r="5" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A5" s="9">
         <v>35521</v>
       </c>
@@ -721,7 +724,7 @@
       <c r="L5" s="12"/>
       <c r="N5" s="21"/>
     </row>
-    <row r="6" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A6" s="9">
         <v>35551</v>
       </c>
@@ -751,7 +754,7 @@
       <c r="L6" s="12"/>
       <c r="N6" s="21"/>
     </row>
-    <row r="7" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A7" s="9">
         <v>35582</v>
       </c>
@@ -781,7 +784,7 @@
       <c r="L7" s="12"/>
       <c r="N7" s="21"/>
     </row>
-    <row r="8" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A8" s="9">
         <v>35612</v>
       </c>
@@ -811,7 +814,7 @@
       <c r="L8" s="12"/>
       <c r="N8" s="21"/>
     </row>
-    <row r="9" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A9" s="9">
         <v>35643</v>
       </c>
@@ -841,7 +844,7 @@
       <c r="L9" s="12"/>
       <c r="N9" s="21"/>
     </row>
-    <row r="10" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A10" s="9">
         <v>35674</v>
       </c>
@@ -871,7 +874,7 @@
       <c r="L10" s="12"/>
       <c r="N10" s="21"/>
     </row>
-    <row r="11" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A11" s="9">
         <v>35704</v>
       </c>
@@ -901,7 +904,7 @@
       <c r="L11" s="12"/>
       <c r="N11" s="21"/>
     </row>
-    <row r="12" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A12" s="9">
         <v>35735</v>
       </c>
@@ -931,7 +934,7 @@
       <c r="L12" s="12"/>
       <c r="N12" s="21"/>
     </row>
-    <row r="13" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A13" s="9">
         <v>35765</v>
       </c>
@@ -961,7 +964,7 @@
       <c r="L13" s="12"/>
       <c r="N13" s="21"/>
     </row>
-    <row r="14" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A14" s="9">
         <v>35796</v>
       </c>
@@ -991,7 +994,7 @@
       <c r="L14" s="12"/>
       <c r="N14" s="21"/>
     </row>
-    <row r="15" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A15" s="9">
         <v>35827</v>
       </c>
@@ -1021,7 +1024,7 @@
       <c r="L15" s="12"/>
       <c r="N15" s="21"/>
     </row>
-    <row r="16" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A16" s="9">
         <v>35855</v>
       </c>
@@ -1051,7 +1054,7 @@
       <c r="L16" s="12"/>
       <c r="N16" s="21"/>
     </row>
-    <row r="17" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A17" s="9">
         <v>35886</v>
       </c>
@@ -1081,7 +1084,7 @@
       <c r="L17" s="12"/>
       <c r="N17" s="21"/>
     </row>
-    <row r="18" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A18" s="9">
         <v>35916</v>
       </c>
@@ -1111,7 +1114,7 @@
       <c r="L18" s="12"/>
       <c r="N18" s="21"/>
     </row>
-    <row r="19" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A19" s="9">
         <v>35947</v>
       </c>
@@ -1141,7 +1144,7 @@
       <c r="L19" s="12"/>
       <c r="N19" s="21"/>
     </row>
-    <row r="20" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A20" s="9">
         <v>35977</v>
       </c>
@@ -1171,7 +1174,7 @@
       <c r="L20" s="12"/>
       <c r="N20" s="21"/>
     </row>
-    <row r="21" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A21" s="9">
         <v>36008</v>
       </c>
@@ -1201,7 +1204,7 @@
       <c r="L21" s="12"/>
       <c r="N21" s="21"/>
     </row>
-    <row r="22" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A22" s="9">
         <v>36039</v>
       </c>
@@ -1231,7 +1234,7 @@
       <c r="L22" s="12"/>
       <c r="N22" s="21"/>
     </row>
-    <row r="23" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A23" s="9">
         <v>36069</v>
       </c>
@@ -1261,7 +1264,7 @@
       <c r="L23" s="12"/>
       <c r="N23" s="21"/>
     </row>
-    <row r="24" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A24" s="9">
         <v>36100</v>
       </c>
@@ -1291,7 +1294,7 @@
       <c r="L24" s="12"/>
       <c r="N24" s="21"/>
     </row>
-    <row r="25" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A25" s="9">
         <v>36130</v>
       </c>
@@ -1321,7 +1324,7 @@
       <c r="L25" s="12"/>
       <c r="N25" s="21"/>
     </row>
-    <row r="26" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A26" s="9">
         <v>36161</v>
       </c>
@@ -1351,7 +1354,7 @@
       <c r="L26" s="12"/>
       <c r="N26" s="21"/>
     </row>
-    <row r="27" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A27" s="9">
         <v>36192</v>
       </c>
@@ -1381,7 +1384,7 @@
       <c r="L27" s="12"/>
       <c r="N27" s="21"/>
     </row>
-    <row r="28" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A28" s="9">
         <v>36220</v>
       </c>
@@ -1411,7 +1414,7 @@
       <c r="L28" s="12"/>
       <c r="N28" s="21"/>
     </row>
-    <row r="29" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A29" s="9">
         <v>36251</v>
       </c>
@@ -1441,7 +1444,7 @@
       <c r="L29" s="12"/>
       <c r="N29" s="21"/>
     </row>
-    <row r="30" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A30" s="9">
         <v>36281</v>
       </c>
@@ -1471,7 +1474,7 @@
       <c r="L30" s="12"/>
       <c r="N30" s="21"/>
     </row>
-    <row r="31" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A31" s="9">
         <v>36312</v>
       </c>
@@ -1501,7 +1504,7 @@
       <c r="L31" s="12"/>
       <c r="N31" s="21"/>
     </row>
-    <row r="32" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A32" s="9">
         <v>36342</v>
       </c>
@@ -1531,7 +1534,7 @@
       <c r="L32" s="12"/>
       <c r="N32" s="21"/>
     </row>
-    <row r="33" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A33" s="9">
         <v>36373</v>
       </c>
@@ -1561,7 +1564,7 @@
       <c r="L33" s="12"/>
       <c r="N33" s="21"/>
     </row>
-    <row r="34" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A34" s="9">
         <v>36404</v>
       </c>
@@ -1591,7 +1594,7 @@
       <c r="L34" s="12"/>
       <c r="N34" s="21"/>
     </row>
-    <row r="35" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A35" s="9">
         <v>36434</v>
       </c>
@@ -1621,7 +1624,7 @@
       <c r="L35" s="12"/>
       <c r="N35" s="21"/>
     </row>
-    <row r="36" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A36" s="9">
         <v>36465</v>
       </c>
@@ -1651,7 +1654,7 @@
       <c r="L36" s="12"/>
       <c r="N36" s="21"/>
     </row>
-    <row r="37" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A37" s="9">
         <v>36495</v>
       </c>
@@ -1681,7 +1684,7 @@
       <c r="L37" s="12"/>
       <c r="N37" s="21"/>
     </row>
-    <row r="38" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A38" s="9">
         <v>36526</v>
       </c>
@@ -1711,7 +1714,7 @@
       <c r="L38" s="12"/>
       <c r="N38" s="21"/>
     </row>
-    <row r="39" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A39" s="9">
         <v>36557</v>
       </c>
@@ -1741,7 +1744,7 @@
       <c r="L39" s="12"/>
       <c r="N39" s="21"/>
     </row>
-    <row r="40" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A40" s="9">
         <v>36586</v>
       </c>
@@ -1771,7 +1774,7 @@
       <c r="L40" s="12"/>
       <c r="N40" s="21"/>
     </row>
-    <row r="41" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A41" s="9">
         <v>36617</v>
       </c>
@@ -1801,7 +1804,7 @@
       <c r="L41" s="12"/>
       <c r="N41" s="21"/>
     </row>
-    <row r="42" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A42" s="9">
         <v>36647</v>
       </c>
@@ -1831,7 +1834,7 @@
       <c r="L42" s="12"/>
       <c r="N42" s="21"/>
     </row>
-    <row r="43" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A43" s="9">
         <v>36678</v>
       </c>
@@ -1861,7 +1864,7 @@
       <c r="L43" s="12"/>
       <c r="N43" s="21"/>
     </row>
-    <row r="44" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A44" s="9">
         <v>36708</v>
       </c>
@@ -1891,7 +1894,7 @@
       <c r="L44" s="12"/>
       <c r="N44" s="21"/>
     </row>
-    <row r="45" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A45" s="9">
         <v>36739</v>
       </c>
@@ -1921,7 +1924,7 @@
       <c r="L45" s="12"/>
       <c r="N45" s="21"/>
     </row>
-    <row r="46" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A46" s="9">
         <v>36770</v>
       </c>
@@ -1951,7 +1954,7 @@
       <c r="L46" s="12"/>
       <c r="N46" s="21"/>
     </row>
-    <row r="47" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A47" s="9">
         <v>36800</v>
       </c>
@@ -1981,7 +1984,7 @@
       <c r="L47" s="12"/>
       <c r="N47" s="21"/>
     </row>
-    <row r="48" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A48" s="9">
         <v>36831</v>
       </c>
@@ -2011,7 +2014,7 @@
       <c r="L48" s="12"/>
       <c r="N48" s="21"/>
     </row>
-    <row r="49" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A49" s="9">
         <v>36861</v>
       </c>
@@ -2041,7 +2044,7 @@
       <c r="L49" s="12"/>
       <c r="N49" s="21"/>
     </row>
-    <row r="50" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A50" s="9">
         <v>36892</v>
       </c>
@@ -2071,7 +2074,7 @@
       <c r="L50" s="12"/>
       <c r="N50" s="21"/>
     </row>
-    <row r="51" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A51" s="9">
         <v>36923</v>
       </c>
@@ -2101,7 +2104,7 @@
       <c r="L51" s="12"/>
       <c r="N51" s="21"/>
     </row>
-    <row r="52" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A52" s="9">
         <v>36951</v>
       </c>
@@ -2131,7 +2134,7 @@
       <c r="L52" s="12"/>
       <c r="N52" s="21"/>
     </row>
-    <row r="53" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A53" s="9">
         <v>36982</v>
       </c>
@@ -2161,7 +2164,7 @@
       <c r="L53" s="12"/>
       <c r="N53" s="21"/>
     </row>
-    <row r="54" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A54" s="9">
         <v>37012</v>
       </c>
@@ -2191,7 +2194,7 @@
       <c r="L54" s="12"/>
       <c r="N54" s="21"/>
     </row>
-    <row r="55" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A55" s="9">
         <v>37043</v>
       </c>
@@ -2221,7 +2224,7 @@
       <c r="L55" s="12"/>
       <c r="N55" s="21"/>
     </row>
-    <row r="56" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A56" s="9">
         <v>37073</v>
       </c>
@@ -2251,7 +2254,7 @@
       <c r="L56" s="12"/>
       <c r="N56" s="21"/>
     </row>
-    <row r="57" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A57" s="9">
         <v>37104</v>
       </c>
@@ -2281,7 +2284,7 @@
       <c r="L57" s="12"/>
       <c r="N57" s="21"/>
     </row>
-    <row r="58" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A58" s="9">
         <v>37135</v>
       </c>
@@ -2311,7 +2314,7 @@
       <c r="L58" s="12"/>
       <c r="N58" s="21"/>
     </row>
-    <row r="59" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A59" s="9">
         <v>37165</v>
       </c>
@@ -2341,7 +2344,7 @@
       <c r="L59" s="12"/>
       <c r="N59" s="21"/>
     </row>
-    <row r="60" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A60" s="9">
         <v>37196</v>
       </c>
@@ -2371,7 +2374,7 @@
       <c r="L60" s="12"/>
       <c r="N60" s="21"/>
     </row>
-    <row r="61" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A61" s="9">
         <v>37226</v>
       </c>
@@ -2401,7 +2404,7 @@
       <c r="L61" s="12"/>
       <c r="N61" s="21"/>
     </row>
-    <row r="62" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A62" s="9">
         <v>37258</v>
       </c>
@@ -2431,7 +2434,7 @@
       <c r="L62" s="12"/>
       <c r="N62" s="21"/>
     </row>
-    <row r="63" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A63" s="9">
         <v>37288</v>
       </c>
@@ -2461,7 +2464,7 @@
       <c r="L63" s="12"/>
       <c r="N63" s="21"/>
     </row>
-    <row r="64" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A64" s="9">
         <v>37316</v>
       </c>
@@ -2491,7 +2494,7 @@
       <c r="L64" s="12"/>
       <c r="N64" s="21"/>
     </row>
-    <row r="65" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A65" s="9">
         <v>37347</v>
       </c>
@@ -2521,7 +2524,7 @@
       <c r="L65" s="12"/>
       <c r="N65" s="21"/>
     </row>
-    <row r="66" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A66" s="9">
         <v>37377</v>
       </c>
@@ -2551,7 +2554,7 @@
       <c r="L66" s="12"/>
       <c r="N66" s="21"/>
     </row>
-    <row r="67" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A67" s="9">
         <v>37408</v>
       </c>
@@ -2596,7 +2599,7 @@
       <c r="L67" s="12"/>
       <c r="N67" s="21"/>
     </row>
-    <row r="68" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A68" s="9">
         <v>37438</v>
       </c>
@@ -2626,7 +2629,7 @@
       <c r="L68" s="12"/>
       <c r="N68" s="21"/>
     </row>
-    <row r="69" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A69" s="9">
         <v>37469</v>
       </c>
@@ -2656,7 +2659,7 @@
       <c r="L69" s="12"/>
       <c r="N69" s="21"/>
     </row>
-    <row r="70" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A70" s="9">
         <v>37500</v>
       </c>
@@ -2686,7 +2689,7 @@
       <c r="L70" s="12"/>
       <c r="N70" s="21"/>
     </row>
-    <row r="71" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A71" s="9">
         <v>37530</v>
       </c>
@@ -2716,7 +2719,7 @@
       <c r="L71" s="12"/>
       <c r="N71" s="21"/>
     </row>
-    <row r="72" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A72" s="9">
         <v>37561</v>
       </c>
@@ -2746,7 +2749,7 @@
       <c r="L72" s="12"/>
       <c r="N72" s="21"/>
     </row>
-    <row r="73" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A73" s="9">
         <v>37591</v>
       </c>
@@ -2776,7 +2779,7 @@
       <c r="L73" s="12"/>
       <c r="N73" s="21"/>
     </row>
-    <row r="74" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A74" s="9">
         <v>37622</v>
       </c>
@@ -2806,7 +2809,7 @@
       <c r="L74" s="12"/>
       <c r="N74" s="21"/>
     </row>
-    <row r="75" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A75" s="9">
         <v>37653</v>
       </c>
@@ -2836,7 +2839,7 @@
       <c r="L75" s="12"/>
       <c r="N75" s="21"/>
     </row>
-    <row r="76" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A76" s="9">
         <v>37681</v>
       </c>
@@ -2866,7 +2869,7 @@
       <c r="L76" s="12"/>
       <c r="N76" s="21"/>
     </row>
-    <row r="77" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A77" s="9">
         <v>37712</v>
       </c>
@@ -2896,7 +2899,7 @@
       <c r="L77" s="12"/>
       <c r="N77" s="21"/>
     </row>
-    <row r="78" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A78" s="9">
         <v>37742</v>
       </c>
@@ -2926,7 +2929,7 @@
       <c r="L78" s="12"/>
       <c r="N78" s="21"/>
     </row>
-    <row r="79" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A79" s="9">
         <v>37773</v>
       </c>
@@ -2956,7 +2959,7 @@
       <c r="L79" s="12"/>
       <c r="N79" s="21"/>
     </row>
-    <row r="80" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A80" s="9">
         <v>37803</v>
       </c>
@@ -2986,7 +2989,7 @@
       <c r="L80" s="12"/>
       <c r="N80" s="21"/>
     </row>
-    <row r="81" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A81" s="9">
         <v>37834</v>
       </c>
@@ -3016,7 +3019,7 @@
       <c r="L81" s="12"/>
       <c r="N81" s="21"/>
     </row>
-    <row r="82" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A82" s="9">
         <v>37865</v>
       </c>
@@ -3046,7 +3049,7 @@
       <c r="L82" s="12"/>
       <c r="N82" s="21"/>
     </row>
-    <row r="83" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A83" s="9">
         <v>37895</v>
       </c>
@@ -3076,7 +3079,7 @@
       <c r="L83" s="12"/>
       <c r="N83" s="21"/>
     </row>
-    <row r="84" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A84" s="9">
         <v>37926</v>
       </c>
@@ -3106,7 +3109,7 @@
       <c r="L84" s="12"/>
       <c r="N84" s="21"/>
     </row>
-    <row r="85" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A85" s="9">
         <v>37956</v>
       </c>
@@ -3136,7 +3139,7 @@
       <c r="L85" s="12"/>
       <c r="N85" s="21"/>
     </row>
-    <row r="86" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A86" s="9">
         <v>37987</v>
       </c>
@@ -3166,7 +3169,7 @@
       <c r="L86" s="12"/>
       <c r="N86" s="21"/>
     </row>
-    <row r="87" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A87" s="9">
         <v>38018</v>
       </c>
@@ -3196,7 +3199,7 @@
       <c r="L87" s="12"/>
       <c r="N87" s="21"/>
     </row>
-    <row r="88" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A88" s="9">
         <v>38047</v>
       </c>
@@ -3226,7 +3229,7 @@
       <c r="L88" s="12"/>
       <c r="N88" s="21"/>
     </row>
-    <row r="89" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A89" s="9">
         <v>38078</v>
       </c>
@@ -3256,7 +3259,7 @@
       <c r="L89" s="12"/>
       <c r="N89" s="21"/>
     </row>
-    <row r="90" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A90" s="9">
         <v>38108</v>
       </c>
@@ -3286,7 +3289,7 @@
       <c r="L90" s="12"/>
       <c r="N90" s="21"/>
     </row>
-    <row r="91" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A91" s="9">
         <v>38139</v>
       </c>
@@ -3316,7 +3319,7 @@
       <c r="L91" s="12"/>
       <c r="N91" s="21"/>
     </row>
-    <row r="92" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A92" s="9">
         <v>38169</v>
       </c>
@@ -3346,7 +3349,7 @@
       <c r="L92" s="12"/>
       <c r="N92" s="21"/>
     </row>
-    <row r="93" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A93" s="9">
         <v>38200</v>
       </c>
@@ -3376,7 +3379,7 @@
       <c r="L93" s="12"/>
       <c r="N93" s="21"/>
     </row>
-    <row r="94" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A94" s="9">
         <v>38231</v>
       </c>
@@ -3406,7 +3409,7 @@
       <c r="L94" s="12"/>
       <c r="N94" s="21"/>
     </row>
-    <row r="95" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A95" s="9">
         <v>38261</v>
       </c>
@@ -3436,7 +3439,7 @@
       <c r="L95" s="12"/>
       <c r="N95" s="21"/>
     </row>
-    <row r="96" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A96" s="9">
         <v>38292</v>
       </c>
@@ -3466,7 +3469,7 @@
       <c r="L96" s="12"/>
       <c r="N96" s="21"/>
     </row>
-    <row r="97" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A97" s="9">
         <v>38322</v>
       </c>
@@ -3496,7 +3499,7 @@
       <c r="L97" s="12"/>
       <c r="N97" s="21"/>
     </row>
-    <row r="98" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A98" s="9">
         <v>38353</v>
       </c>
@@ -3526,7 +3529,7 @@
       <c r="L98" s="12"/>
       <c r="N98" s="21"/>
     </row>
-    <row r="99" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A99" s="9">
         <v>38384</v>
       </c>
@@ -3556,7 +3559,7 @@
       <c r="L99" s="12"/>
       <c r="N99" s="21"/>
     </row>
-    <row r="100" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A100" s="9">
         <v>38412</v>
       </c>
@@ -3586,7 +3589,7 @@
       <c r="L100" s="12"/>
       <c r="N100" s="21"/>
     </row>
-    <row r="101" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A101" s="9">
         <v>38443</v>
       </c>
@@ -3616,7 +3619,7 @@
       <c r="L101" s="12"/>
       <c r="N101" s="21"/>
     </row>
-    <row r="102" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A102" s="9">
         <v>38473</v>
       </c>
@@ -3646,7 +3649,7 @@
       <c r="L102" s="12"/>
       <c r="N102" s="21"/>
     </row>
-    <row r="103" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A103" s="9">
         <v>38504</v>
       </c>
@@ -3676,7 +3679,7 @@
       <c r="L103" s="12"/>
       <c r="N103" s="21"/>
     </row>
-    <row r="104" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A104" s="9">
         <v>38534</v>
       </c>
@@ -3706,7 +3709,7 @@
       <c r="L104" s="12"/>
       <c r="N104" s="21"/>
     </row>
-    <row r="105" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A105" s="9">
         <v>38565</v>
       </c>
@@ -3736,7 +3739,7 @@
       <c r="L105" s="12"/>
       <c r="N105" s="21"/>
     </row>
-    <row r="106" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A106" s="9">
         <v>38596</v>
       </c>
@@ -3766,7 +3769,7 @@
       <c r="L106" s="12"/>
       <c r="N106" s="21"/>
     </row>
-    <row r="107" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A107" s="9">
         <v>38626</v>
       </c>
@@ -3796,7 +3799,7 @@
       <c r="L107" s="12"/>
       <c r="N107" s="21"/>
     </row>
-    <row r="108" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A108" s="9">
         <v>38657</v>
       </c>
@@ -3826,7 +3829,7 @@
       <c r="L108" s="12"/>
       <c r="N108" s="21"/>
     </row>
-    <row r="109" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A109" s="9">
         <v>38687</v>
       </c>
@@ -3856,7 +3859,7 @@
       <c r="L109" s="12"/>
       <c r="N109" s="21"/>
     </row>
-    <row r="110" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="110" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A110" s="9">
         <v>38718</v>
       </c>
@@ -3886,7 +3889,7 @@
       <c r="L110" s="12"/>
       <c r="N110" s="21"/>
     </row>
-    <row r="111" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="111" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A111" s="9">
         <v>38749</v>
       </c>
@@ -3916,7 +3919,7 @@
       <c r="L111" s="12"/>
       <c r="N111" s="21"/>
     </row>
-    <row r="112" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="112" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A112" s="9">
         <v>38777</v>
       </c>
@@ -3946,7 +3949,7 @@
       <c r="L112" s="12"/>
       <c r="N112" s="21"/>
     </row>
-    <row r="113" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="113" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A113" s="9">
         <v>38808</v>
       </c>
@@ -3976,7 +3979,7 @@
       <c r="L113" s="12"/>
       <c r="N113" s="21"/>
     </row>
-    <row r="114" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="114" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A114" s="9">
         <v>38838</v>
       </c>
@@ -4006,7 +4009,7 @@
       <c r="L114" s="12"/>
       <c r="N114" s="21"/>
     </row>
-    <row r="115" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="115" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A115" s="9">
         <v>38869</v>
       </c>
@@ -4036,7 +4039,7 @@
       <c r="L115" s="12"/>
       <c r="N115" s="21"/>
     </row>
-    <row r="116" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="116" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A116" s="9">
         <v>38899</v>
       </c>
@@ -4066,7 +4069,7 @@
       <c r="L116" s="12"/>
       <c r="N116" s="21"/>
     </row>
-    <row r="117" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="117" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A117" s="9">
         <v>38930</v>
       </c>
@@ -4096,7 +4099,7 @@
       <c r="L117" s="12"/>
       <c r="N117" s="21"/>
     </row>
-    <row r="118" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="118" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A118" s="9">
         <v>38961</v>
       </c>
@@ -4126,7 +4129,7 @@
       <c r="L118" s="12"/>
       <c r="N118" s="21"/>
     </row>
-    <row r="119" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="119" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A119" s="9">
         <v>38991</v>
       </c>
@@ -4156,7 +4159,7 @@
       <c r="L119" s="12"/>
       <c r="N119" s="21"/>
     </row>
-    <row r="120" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="120" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A120" s="9">
         <v>39022</v>
       </c>
@@ -4186,7 +4189,7 @@
       <c r="L120" s="12"/>
       <c r="N120" s="21"/>
     </row>
-    <row r="121" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="121" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A121" s="9">
         <v>39052</v>
       </c>
@@ -4216,7 +4219,7 @@
       <c r="L121" s="12"/>
       <c r="N121" s="21"/>
     </row>
-    <row r="122" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="122" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A122" s="9">
         <v>39083</v>
       </c>
@@ -4246,7 +4249,7 @@
       <c r="L122" s="12"/>
       <c r="N122" s="21"/>
     </row>
-    <row r="123" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="123" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A123" s="9">
         <v>39114</v>
       </c>
@@ -4276,7 +4279,7 @@
       <c r="L123" s="12"/>
       <c r="N123" s="21"/>
     </row>
-    <row r="124" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="124" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A124" s="9">
         <v>39142</v>
       </c>
@@ -4306,7 +4309,7 @@
       <c r="L124" s="12"/>
       <c r="N124" s="21"/>
     </row>
-    <row r="125" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="125" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A125" s="9">
         <v>39173</v>
       </c>
@@ -4336,7 +4339,7 @@
       <c r="L125" s="12"/>
       <c r="N125" s="21"/>
     </row>
-    <row r="126" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="126" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A126" s="9">
         <v>39203</v>
       </c>
@@ -4366,7 +4369,7 @@
       <c r="L126" s="12"/>
       <c r="N126" s="21"/>
     </row>
-    <row r="127" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="127" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A127" s="9">
         <v>39234</v>
       </c>
@@ -4396,7 +4399,7 @@
       <c r="L127" s="12"/>
       <c r="N127" s="21"/>
     </row>
-    <row r="128" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="128" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A128" s="9">
         <v>39264</v>
       </c>
@@ -4426,7 +4429,7 @@
       <c r="L128" s="12"/>
       <c r="N128" s="21"/>
     </row>
-    <row r="129" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="129" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A129" s="9">
         <v>39295</v>
       </c>
@@ -4456,7 +4459,7 @@
       <c r="L129" s="12"/>
       <c r="N129" s="21"/>
     </row>
-    <row r="130" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="130" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A130" s="9">
         <v>39326</v>
       </c>
@@ -4486,7 +4489,7 @@
       <c r="L130" s="12"/>
       <c r="N130" s="21"/>
     </row>
-    <row r="131" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="131" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A131" s="9">
         <v>39356</v>
       </c>
@@ -4531,7 +4534,7 @@
       <c r="L131" s="12"/>
       <c r="N131" s="21"/>
     </row>
-    <row r="132" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="132" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A132" s="9">
         <v>39387</v>
       </c>
@@ -4561,7 +4564,7 @@
       <c r="L132" s="12"/>
       <c r="N132" s="21"/>
     </row>
-    <row r="133" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="133" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A133" s="9">
         <v>39417</v>
       </c>
@@ -4591,7 +4594,7 @@
       <c r="L133" s="12"/>
       <c r="N133" s="21"/>
     </row>
-    <row r="134" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="134" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A134" s="9">
         <v>39448</v>
       </c>
@@ -4621,7 +4624,7 @@
       <c r="L134" s="12"/>
       <c r="N134" s="21"/>
     </row>
-    <row r="135" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="135" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A135" s="9">
         <v>39479</v>
       </c>
@@ -4651,7 +4654,7 @@
       <c r="L135" s="12"/>
       <c r="N135" s="21"/>
     </row>
-    <row r="136" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="136" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A136" s="9">
         <v>39508</v>
       </c>
@@ -4681,7 +4684,7 @@
       <c r="L136" s="12"/>
       <c r="N136" s="21"/>
     </row>
-    <row r="137" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="137" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A137" s="9">
         <v>39539</v>
       </c>
@@ -4711,7 +4714,7 @@
       <c r="L137" s="12"/>
       <c r="N137" s="21"/>
     </row>
-    <row r="138" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="138" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A138" s="9">
         <v>39569</v>
       </c>
@@ -4741,7 +4744,7 @@
       <c r="L138" s="12"/>
       <c r="N138" s="21"/>
     </row>
-    <row r="139" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="139" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A139" s="9">
         <v>39600</v>
       </c>
@@ -4771,7 +4774,7 @@
       <c r="L139" s="12"/>
       <c r="N139" s="21"/>
     </row>
-    <row r="140" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="140" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A140" s="9">
         <v>39630</v>
       </c>
@@ -4801,7 +4804,7 @@
       <c r="L140" s="12"/>
       <c r="N140" s="21"/>
     </row>
-    <row r="141" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="141" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A141" s="9">
         <v>39661</v>
       </c>
@@ -4831,7 +4834,7 @@
       <c r="L141" s="12"/>
       <c r="N141" s="21"/>
     </row>
-    <row r="142" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="142" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A142" s="9">
         <v>39692</v>
       </c>
@@ -4861,7 +4864,7 @@
       <c r="L142" s="12"/>
       <c r="N142" s="21"/>
     </row>
-    <row r="143" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="143" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A143" s="9">
         <v>39722</v>
       </c>
@@ -4891,7 +4894,7 @@
       <c r="L143" s="12"/>
       <c r="N143" s="21"/>
     </row>
-    <row r="144" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="144" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A144" s="9">
         <v>39753</v>
       </c>
@@ -4921,7 +4924,7 @@
       <c r="L144" s="12"/>
       <c r="N144" s="21"/>
     </row>
-    <row r="145" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="145" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A145" s="9">
         <v>39783</v>
       </c>
@@ -4951,7 +4954,7 @@
       <c r="L145" s="12"/>
       <c r="N145" s="21"/>
     </row>
-    <row r="146" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="146" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A146" s="9">
         <v>39814</v>
       </c>
@@ -4981,7 +4984,7 @@
       <c r="L146" s="12"/>
       <c r="N146" s="21"/>
     </row>
-    <row r="147" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="147" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A147" s="9">
         <v>39845</v>
       </c>
@@ -5011,7 +5014,7 @@
       <c r="L147" s="12"/>
       <c r="N147" s="21"/>
     </row>
-    <row r="148" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="148" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A148" s="9">
         <v>39873</v>
       </c>
@@ -5041,7 +5044,7 @@
       <c r="L148" s="12"/>
       <c r="N148" s="21"/>
     </row>
-    <row r="149" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="149" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A149" s="9">
         <v>39904</v>
       </c>
@@ -5071,7 +5074,7 @@
       <c r="L149" s="12"/>
       <c r="N149" s="21"/>
     </row>
-    <row r="150" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="150" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A150" s="9">
         <v>39934</v>
       </c>
@@ -5101,7 +5104,7 @@
       <c r="L150" s="12"/>
       <c r="N150" s="21"/>
     </row>
-    <row r="151" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="151" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A151" s="9">
         <v>39965</v>
       </c>
@@ -5131,7 +5134,7 @@
       <c r="L151" s="12"/>
       <c r="N151" s="21"/>
     </row>
-    <row r="152" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="152" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A152" s="9">
         <v>39995</v>
       </c>
@@ -5161,7 +5164,7 @@
       <c r="L152" s="12"/>
       <c r="N152" s="21"/>
     </row>
-    <row r="153" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="153" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A153" s="9">
         <v>40026</v>
       </c>
@@ -5191,7 +5194,7 @@
       <c r="L153" s="12"/>
       <c r="N153" s="21"/>
     </row>
-    <row r="154" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="154" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A154" s="9">
         <v>40057</v>
       </c>
@@ -5221,7 +5224,7 @@
       <c r="L154" s="12"/>
       <c r="N154" s="21"/>
     </row>
-    <row r="155" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="155" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A155" s="9">
         <v>40087</v>
       </c>
@@ -5251,7 +5254,7 @@
       <c r="L155" s="12"/>
       <c r="N155" s="21"/>
     </row>
-    <row r="156" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="156" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A156" s="9">
         <v>40118</v>
       </c>
@@ -5281,7 +5284,7 @@
       <c r="L156" s="12"/>
       <c r="N156" s="21"/>
     </row>
-    <row r="157" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="157" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A157" s="9">
         <v>40148</v>
       </c>
@@ -5311,7 +5314,7 @@
       <c r="L157" s="12"/>
       <c r="N157" s="21"/>
     </row>
-    <row r="158" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="158" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A158" s="9">
         <v>40179</v>
       </c>
@@ -5341,7 +5344,7 @@
       <c r="L158" s="12"/>
       <c r="N158" s="21"/>
     </row>
-    <row r="159" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="159" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A159" s="9">
         <v>40210</v>
       </c>
@@ -5371,7 +5374,7 @@
       <c r="L159" s="12"/>
       <c r="N159" s="21"/>
     </row>
-    <row r="160" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="160" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A160" s="9">
         <v>40238</v>
       </c>
@@ -5401,7 +5404,7 @@
       <c r="L160" s="12"/>
       <c r="N160" s="21"/>
     </row>
-    <row r="161" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="161" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A161" s="9">
         <v>40269</v>
       </c>
@@ -5431,7 +5434,7 @@
       <c r="L161" s="12"/>
       <c r="N161" s="21"/>
     </row>
-    <row r="162" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="162" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A162" s="9">
         <v>40299</v>
       </c>
@@ -5461,7 +5464,7 @@
       <c r="L162" s="12"/>
       <c r="N162" s="21"/>
     </row>
-    <row r="163" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="163" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A163" s="9">
         <v>40330</v>
       </c>
@@ -5491,7 +5494,7 @@
       <c r="L163" s="12"/>
       <c r="N163" s="21"/>
     </row>
-    <row r="164" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="164" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A164" s="9">
         <v>40360</v>
       </c>
@@ -5521,7 +5524,7 @@
       <c r="L164" s="12"/>
       <c r="N164" s="21"/>
     </row>
-    <row r="165" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="165" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A165" s="9">
         <v>40391</v>
       </c>
@@ -5551,7 +5554,7 @@
       <c r="L165" s="12"/>
       <c r="N165" s="21"/>
     </row>
-    <row r="166" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="166" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A166" s="9">
         <v>40422</v>
       </c>
@@ -5581,7 +5584,7 @@
       <c r="L166" s="12"/>
       <c r="N166" s="21"/>
     </row>
-    <row r="167" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="167" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A167" s="9">
         <v>40452</v>
       </c>
@@ -5611,7 +5614,7 @@
       <c r="L167" s="12"/>
       <c r="N167" s="21"/>
     </row>
-    <row r="168" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="168" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A168" s="9">
         <v>40483</v>
       </c>
@@ -5641,7 +5644,7 @@
       <c r="L168" s="12"/>
       <c r="N168" s="21"/>
     </row>
-    <row r="169" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="169" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A169" s="9">
         <v>40513</v>
       </c>
@@ -5671,7 +5674,7 @@
       <c r="L169" s="12"/>
       <c r="N169" s="21"/>
     </row>
-    <row r="170" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="170" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A170" s="9">
         <v>40544</v>
       </c>
@@ -5702,7 +5705,7 @@
       <c r="N170" s="13"/>
       <c r="O170" s="13"/>
     </row>
-    <row r="171" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="171" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A171" s="9">
         <v>40575</v>
       </c>
@@ -5733,7 +5736,7 @@
       <c r="N171" s="13"/>
       <c r="O171" s="13"/>
     </row>
-    <row r="172" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="172" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A172" s="9">
         <v>40603</v>
       </c>
@@ -5764,7 +5767,7 @@
       <c r="N172" s="13"/>
       <c r="O172" s="13"/>
     </row>
-    <row r="173" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="173" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A173" s="9">
         <v>40634</v>
       </c>
@@ -5795,7 +5798,7 @@
       <c r="N173" s="13"/>
       <c r="O173" s="13"/>
     </row>
-    <row r="174" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="174" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A174" s="9">
         <v>40664</v>
       </c>
@@ -5826,7 +5829,7 @@
       <c r="N174" s="13"/>
       <c r="O174" s="13"/>
     </row>
-    <row r="175" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="175" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A175" s="9">
         <v>40695</v>
       </c>
@@ -5857,7 +5860,7 @@
       <c r="N175" s="13"/>
       <c r="O175" s="13"/>
     </row>
-    <row r="176" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="176" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A176" s="9">
         <v>40725</v>
       </c>
@@ -5888,7 +5891,7 @@
       <c r="N176" s="13"/>
       <c r="O176" s="13"/>
     </row>
-    <row r="177" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="177" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A177" s="9">
         <v>40756</v>
       </c>
@@ -5919,7 +5922,7 @@
       <c r="N177" s="13"/>
       <c r="O177" s="13"/>
     </row>
-    <row r="178" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="178" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A178" s="9">
         <v>40787</v>
       </c>
@@ -5950,7 +5953,7 @@
       <c r="N178" s="13"/>
       <c r="O178" s="13"/>
     </row>
-    <row r="179" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="179" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A179" s="9">
         <v>40817</v>
       </c>
@@ -5981,7 +5984,7 @@
       <c r="N179" s="13"/>
       <c r="O179" s="13"/>
     </row>
-    <row r="180" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="180" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A180" s="9">
         <v>40848</v>
       </c>
@@ -6012,7 +6015,7 @@
       <c r="N180" s="13"/>
       <c r="O180" s="13"/>
     </row>
-    <row r="181" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="181" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A181" s="9">
         <v>40878</v>
       </c>
@@ -6043,7 +6046,7 @@
       <c r="N181" s="13"/>
       <c r="O181" s="13"/>
     </row>
-    <row r="182" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="182" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A182" s="9">
         <v>40909</v>
       </c>
@@ -6074,7 +6077,7 @@
       <c r="N182" s="13"/>
       <c r="O182" s="13"/>
     </row>
-    <row r="183" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="183" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A183" s="9">
         <v>40940</v>
       </c>
@@ -6105,7 +6108,7 @@
       <c r="N183" s="13"/>
       <c r="O183" s="13"/>
     </row>
-    <row r="184" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="184" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A184" s="9">
         <v>40969</v>
       </c>
@@ -6136,7 +6139,7 @@
       <c r="N184" s="13"/>
       <c r="O184" s="13"/>
     </row>
-    <row r="185" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="185" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A185" s="9">
         <v>41000</v>
       </c>
@@ -6167,7 +6170,7 @@
       <c r="N185" s="13"/>
       <c r="O185" s="13"/>
     </row>
-    <row r="186" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="186" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A186" s="9">
         <v>41030</v>
       </c>
@@ -6198,7 +6201,7 @@
       <c r="N186" s="13"/>
       <c r="O186" s="13"/>
     </row>
-    <row r="187" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="187" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A187" s="9">
         <v>41061</v>
       </c>
@@ -6229,7 +6232,7 @@
       <c r="N187" s="13"/>
       <c r="O187" s="13"/>
     </row>
-    <row r="188" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="188" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A188" s="9">
         <v>41091</v>
       </c>
@@ -6260,7 +6263,7 @@
       <c r="N188" s="13"/>
       <c r="O188" s="13"/>
     </row>
-    <row r="189" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="189" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A189" s="9">
         <v>41122</v>
       </c>
@@ -6291,7 +6294,7 @@
       <c r="N189" s="13"/>
       <c r="O189" s="13"/>
     </row>
-    <row r="190" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="190" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A190" s="9">
         <v>41153</v>
       </c>
@@ -6322,7 +6325,7 @@
       <c r="N190" s="13"/>
       <c r="O190" s="13"/>
     </row>
-    <row r="191" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="191" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A191" s="9">
         <v>41183</v>
       </c>
@@ -6353,7 +6356,7 @@
       <c r="N191" s="13"/>
       <c r="O191" s="13"/>
     </row>
-    <row r="192" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="192" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A192" s="9">
         <v>41214</v>
       </c>
@@ -6384,7 +6387,7 @@
       <c r="N192" s="13"/>
       <c r="O192" s="13"/>
     </row>
-    <row r="193" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="193" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A193" s="9">
         <v>41244</v>
       </c>
@@ -6415,7 +6418,7 @@
       <c r="N193" s="13"/>
       <c r="O193" s="13"/>
     </row>
-    <row r="194" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="194" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A194" s="9">
         <v>41275</v>
       </c>
@@ -6446,7 +6449,7 @@
       <c r="N194" s="13"/>
       <c r="O194" s="13"/>
     </row>
-    <row r="195" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="195" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A195" s="9">
         <v>41306</v>
       </c>
@@ -6492,7 +6495,7 @@
       <c r="N195" s="13"/>
       <c r="O195" s="13"/>
     </row>
-    <row r="196" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="196" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A196" s="9">
         <v>41334</v>
       </c>
@@ -6523,7 +6526,7 @@
       <c r="N196" s="13"/>
       <c r="O196" s="13"/>
     </row>
-    <row r="197" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="197" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A197" s="9">
         <v>41365</v>
       </c>
@@ -6554,7 +6557,7 @@
       <c r="N197" s="13"/>
       <c r="O197" s="13"/>
     </row>
-    <row r="198" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="198" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A198" s="9">
         <v>41395</v>
       </c>
@@ -6585,7 +6588,7 @@
       <c r="N198" s="13"/>
       <c r="O198" s="13"/>
     </row>
-    <row r="199" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="199" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A199" s="9">
         <v>41426</v>
       </c>
@@ -6616,7 +6619,7 @@
       <c r="N199" s="13"/>
       <c r="O199" s="13"/>
     </row>
-    <row r="200" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="200" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A200" s="9">
         <v>41456</v>
       </c>
@@ -6647,7 +6650,7 @@
       <c r="N200" s="13"/>
       <c r="O200" s="13"/>
     </row>
-    <row r="201" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="201" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A201" s="9">
         <v>41487</v>
       </c>
@@ -6678,7 +6681,7 @@
       <c r="N201" s="13"/>
       <c r="O201" s="13"/>
     </row>
-    <row r="202" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="202" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A202" s="9">
         <v>41518</v>
       </c>
@@ -6709,7 +6712,7 @@
       <c r="N202" s="13"/>
       <c r="O202" s="13"/>
     </row>
-    <row r="203" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="203" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A203" s="9">
         <v>41548</v>
       </c>
@@ -6740,7 +6743,7 @@
       <c r="N203" s="13"/>
       <c r="O203" s="13"/>
     </row>
-    <row r="204" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="204" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A204" s="9">
         <v>41579</v>
       </c>
@@ -6771,7 +6774,7 @@
       <c r="N204" s="13"/>
       <c r="O204" s="13"/>
     </row>
-    <row r="205" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="205" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A205" s="9">
         <v>41609</v>
       </c>
@@ -6802,7 +6805,7 @@
       <c r="N205" s="13"/>
       <c r="O205" s="13"/>
     </row>
-    <row r="206" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="206" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A206" s="9">
         <v>41640</v>
       </c>
@@ -6833,7 +6836,7 @@
       <c r="N206" s="13"/>
       <c r="O206" s="13"/>
     </row>
-    <row r="207" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="207" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A207" s="9">
         <v>41671</v>
       </c>
@@ -6864,7 +6867,7 @@
       <c r="N207" s="13"/>
       <c r="O207" s="13"/>
     </row>
-    <row r="208" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="208" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A208" s="9">
         <v>41699</v>
       </c>
@@ -6895,7 +6898,7 @@
       <c r="N208" s="13"/>
       <c r="O208" s="13"/>
     </row>
-    <row r="209" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="209" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A209" s="9">
         <v>41730</v>
       </c>
@@ -6926,7 +6929,7 @@
       <c r="N209" s="13"/>
       <c r="O209" s="13"/>
     </row>
-    <row r="210" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="210" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A210" s="9">
         <v>41760</v>
       </c>
@@ -6957,7 +6960,7 @@
       <c r="N210" s="13"/>
       <c r="O210" s="13"/>
     </row>
-    <row r="211" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="211" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A211" s="9">
         <v>41791</v>
       </c>
@@ -6988,7 +6991,7 @@
       <c r="N211" s="13"/>
       <c r="O211" s="13"/>
     </row>
-    <row r="212" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="212" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A212" s="9">
         <v>41821</v>
       </c>
@@ -7019,7 +7022,7 @@
       <c r="N212" s="13"/>
       <c r="O212" s="13"/>
     </row>
-    <row r="213" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="213" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A213" s="9">
         <v>41852</v>
       </c>
@@ -7050,7 +7053,7 @@
       <c r="N213" s="13"/>
       <c r="O213" s="13"/>
     </row>
-    <row r="214" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="214" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A214" s="9">
         <v>41883</v>
       </c>
@@ -7081,7 +7084,7 @@
       <c r="N214" s="13"/>
       <c r="O214" s="13"/>
     </row>
-    <row r="215" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="215" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A215" s="9">
         <v>41913</v>
       </c>
@@ -7112,7 +7115,7 @@
       <c r="N215" s="13"/>
       <c r="O215" s="13"/>
     </row>
-    <row r="216" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="216" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A216" s="9">
         <v>41944</v>
       </c>
@@ -7143,7 +7146,7 @@
       <c r="N216" s="13"/>
       <c r="O216" s="13"/>
     </row>
-    <row r="217" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="217" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A217" s="9">
         <v>41974</v>
       </c>
@@ -7174,7 +7177,7 @@
       <c r="N217" s="13"/>
       <c r="O217" s="13"/>
     </row>
-    <row r="218" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="218" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A218" s="9">
         <v>42005</v>
       </c>
@@ -7213,7 +7216,7 @@
       <c r="N218" s="13"/>
       <c r="O218" s="13"/>
     </row>
-    <row r="219" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="219" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A219" s="9">
         <v>42036</v>
       </c>
@@ -7252,7 +7255,7 @@
       <c r="N219" s="13"/>
       <c r="O219" s="13"/>
     </row>
-    <row r="220" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="220" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A220" s="9">
         <v>42064</v>
       </c>
@@ -7291,7 +7294,7 @@
       <c r="N220" s="13"/>
       <c r="O220" s="13"/>
     </row>
-    <row r="221" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="221" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A221" s="9">
         <v>42095</v>
       </c>
@@ -7330,7 +7333,7 @@
       <c r="N221" s="13"/>
       <c r="O221" s="13"/>
     </row>
-    <row r="222" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="222" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A222" s="9">
         <v>42125</v>
       </c>
@@ -7369,7 +7372,7 @@
       <c r="N222" s="13"/>
       <c r="O222" s="13"/>
     </row>
-    <row r="223" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="223" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A223" s="9">
         <v>42156</v>
       </c>
@@ -7408,7 +7411,7 @@
       <c r="N223" s="13"/>
       <c r="O223" s="13"/>
     </row>
-    <row r="224" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="224" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A224" s="9">
         <v>42186</v>
       </c>
@@ -7447,7 +7450,7 @@
       <c r="N224" s="13"/>
       <c r="O224" s="13"/>
     </row>
-    <row r="225" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="225" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A225" s="9">
         <v>42217</v>
       </c>
@@ -7486,7 +7489,7 @@
       <c r="N225" s="13"/>
       <c r="O225" s="13"/>
     </row>
-    <row r="226" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="226" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A226" s="9">
         <v>42248</v>
       </c>
@@ -7525,7 +7528,7 @@
       <c r="N226" s="13"/>
       <c r="O226" s="13"/>
     </row>
-    <row r="227" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="227" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A227" s="9">
         <v>42278</v>
       </c>
@@ -7564,7 +7567,7 @@
       <c r="N227" s="13"/>
       <c r="O227" s="13"/>
     </row>
-    <row r="228" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="228" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A228" s="9">
         <v>42309</v>
       </c>
@@ -7603,7 +7606,7 @@
       <c r="N228" s="13"/>
       <c r="O228" s="13"/>
     </row>
-    <row r="229" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="229" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A229" s="9">
         <v>42339</v>
       </c>
@@ -7642,7 +7645,7 @@
       <c r="N229" s="13"/>
       <c r="O229" s="13"/>
     </row>
-    <row r="230" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="230" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A230" s="9">
         <v>42370</v>
       </c>
@@ -7681,7 +7684,7 @@
       <c r="N230" s="13"/>
       <c r="O230" s="13"/>
     </row>
-    <row r="231" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="231" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A231" s="9">
         <v>42401</v>
       </c>
@@ -7720,7 +7723,7 @@
       <c r="N231" s="13"/>
       <c r="O231" s="13"/>
     </row>
-    <row r="232" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="232" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A232" s="9">
         <v>42430</v>
       </c>
@@ -7759,7 +7762,7 @@
       <c r="N232" s="13"/>
       <c r="O232" s="13"/>
     </row>
-    <row r="233" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="233" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A233" s="9">
         <v>42461</v>
       </c>
@@ -7798,7 +7801,7 @@
       <c r="N233" s="13"/>
       <c r="O233" s="13"/>
     </row>
-    <row r="234" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="234" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A234" s="9">
         <v>42491</v>
       </c>
@@ -7837,7 +7840,7 @@
       <c r="N234" s="13"/>
       <c r="O234" s="13"/>
     </row>
-    <row r="235" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="235" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A235" s="9">
         <v>42522</v>
       </c>
@@ -7876,7 +7879,7 @@
       <c r="N235" s="13"/>
       <c r="O235" s="13"/>
     </row>
-    <row r="236" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="236" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A236" s="9">
         <v>42552</v>
       </c>
@@ -7915,7 +7918,7 @@
       <c r="N236" s="13"/>
       <c r="O236" s="13"/>
     </row>
-    <row r="237" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="237" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A237" s="9">
         <v>42583</v>
       </c>
@@ -7954,7 +7957,7 @@
       <c r="N237" s="13"/>
       <c r="O237" s="13"/>
     </row>
-    <row r="238" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="238" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A238" s="9">
         <v>42614</v>
       </c>
@@ -7993,7 +7996,7 @@
       <c r="N238" s="13"/>
       <c r="O238" s="13"/>
     </row>
-    <row r="239" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="239" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A239" s="9">
         <v>42644</v>
       </c>
@@ -8032,7 +8035,7 @@
       <c r="N239" s="13"/>
       <c r="O239" s="13"/>
     </row>
-    <row r="240" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="240" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A240" s="9">
         <v>42675</v>
       </c>
@@ -8071,7 +8074,7 @@
       <c r="N240" s="13"/>
       <c r="O240" s="13"/>
     </row>
-    <row r="241" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="241" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A241" s="9">
         <v>42705</v>
       </c>
@@ -8110,7 +8113,7 @@
       <c r="N241" s="13"/>
       <c r="O241" s="13"/>
     </row>
-    <row r="242" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="242" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A242" s="9">
         <v>42736</v>
       </c>
@@ -8149,7 +8152,7 @@
       <c r="N242" s="13"/>
       <c r="O242" s="13"/>
     </row>
-    <row r="243" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="243" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A243" s="9">
         <v>42767</v>
       </c>
@@ -8188,7 +8191,7 @@
       <c r="N243" s="13"/>
       <c r="O243" s="13"/>
     </row>
-    <row r="244" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="244" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A244" s="9">
         <v>42795</v>
       </c>
@@ -8226,7 +8229,7 @@
       <c r="L244" s="12"/>
       <c r="N244" s="21"/>
     </row>
-    <row r="245" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="245" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A245" s="9">
         <v>42826</v>
       </c>
@@ -8264,7 +8267,7 @@
       <c r="L245" s="12"/>
       <c r="N245" s="21"/>
     </row>
-    <row r="246" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="246" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A246" s="9">
         <v>42856</v>
       </c>
@@ -8302,7 +8305,7 @@
       <c r="L246" s="12"/>
       <c r="N246" s="21"/>
     </row>
-    <row r="247" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="247" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A247" s="9">
         <v>42887</v>
       </c>
@@ -8340,7 +8343,7 @@
       <c r="L247" s="12"/>
       <c r="N247" s="21"/>
     </row>
-    <row r="248" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="248" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A248" s="9">
         <v>42917</v>
       </c>
@@ -8378,7 +8381,7 @@
       <c r="L248" s="12"/>
       <c r="N248" s="21"/>
     </row>
-    <row r="249" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="249" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A249" s="9">
         <v>42948</v>
       </c>
@@ -8416,7 +8419,7 @@
       <c r="L249" s="12"/>
       <c r="N249" s="21"/>
     </row>
-    <row r="250" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="250" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A250" s="9">
         <v>42979</v>
       </c>
@@ -8454,7 +8457,7 @@
       <c r="L250" s="12"/>
       <c r="N250" s="21"/>
     </row>
-    <row r="251" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="251" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A251" s="9">
         <v>43009</v>
       </c>
@@ -8492,7 +8495,7 @@
       <c r="L251" s="12"/>
       <c r="N251" s="21"/>
     </row>
-    <row r="252" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="252" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A252" s="9">
         <v>43040</v>
       </c>
@@ -8530,7 +8533,7 @@
       <c r="L252" s="12"/>
       <c r="N252" s="21"/>
     </row>
-    <row r="253" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="253" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A253" s="9">
         <v>43070</v>
       </c>
@@ -8568,7 +8571,7 @@
       <c r="L253" s="12"/>
       <c r="N253" s="21"/>
     </row>
-    <row r="254" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="254" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A254" s="9">
         <v>43101</v>
       </c>
@@ -8606,7 +8609,7 @@
       <c r="L254" s="12"/>
       <c r="N254" s="21"/>
     </row>
-    <row r="255" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="255" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A255" s="9">
         <v>43132</v>
       </c>
@@ -8644,7 +8647,7 @@
       <c r="L255" s="12"/>
       <c r="N255" s="21"/>
     </row>
-    <row r="256" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="256" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A256" s="9">
         <v>43160</v>
       </c>
@@ -8682,7 +8685,7 @@
       <c r="L256" s="12"/>
       <c r="N256" s="21"/>
     </row>
-    <row r="257" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="257" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A257" s="9">
         <v>43191</v>
       </c>
@@ -8720,7 +8723,7 @@
       <c r="L257" s="12"/>
       <c r="N257" s="21"/>
     </row>
-    <row r="258" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="258" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A258" s="9">
         <v>43221</v>
       </c>
@@ -8758,7 +8761,7 @@
       <c r="L258" s="12"/>
       <c r="N258" s="21"/>
     </row>
-    <row r="259" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="259" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A259" s="9">
         <v>43252</v>
       </c>
@@ -8811,7 +8814,7 @@
       <c r="L259" s="12"/>
       <c r="N259" s="21"/>
     </row>
-    <row r="260" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="260" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A260" s="9">
         <v>43282</v>
       </c>
@@ -8849,7 +8852,7 @@
       <c r="L260" s="12"/>
       <c r="N260" s="21"/>
     </row>
-    <row r="261" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="261" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A261" s="9">
         <v>43313</v>
       </c>
@@ -8887,7 +8890,7 @@
       <c r="L261" s="12"/>
       <c r="N261" s="21"/>
     </row>
-    <row r="262" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="262" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A262" s="9">
         <v>43344</v>
       </c>
@@ -8925,7 +8928,7 @@
       <c r="L262" s="12"/>
       <c r="N262" s="21"/>
     </row>
-    <row r="263" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="263" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A263" s="9">
         <v>43374</v>
       </c>
@@ -8963,7 +8966,7 @@
       <c r="L263" s="12"/>
       <c r="N263" s="21"/>
     </row>
-    <row r="264" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="264" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A264" s="9">
         <v>43405</v>
       </c>
@@ -9001,7 +9004,7 @@
       <c r="L264" s="12"/>
       <c r="N264" s="21"/>
     </row>
-    <row r="265" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="265" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A265" s="9">
         <v>43435</v>
       </c>
@@ -9039,7 +9042,7 @@
       <c r="L265" s="12"/>
       <c r="N265" s="21"/>
     </row>
-    <row r="266" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="266" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A266" s="9">
         <v>43466</v>
       </c>
@@ -9077,7 +9080,7 @@
       <c r="L266" s="12"/>
       <c r="N266" s="21"/>
     </row>
-    <row r="267" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="267" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A267" s="9">
         <v>43497</v>
       </c>
@@ -9115,7 +9118,7 @@
       <c r="L267" s="12"/>
       <c r="N267" s="21"/>
     </row>
-    <row r="268" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="268" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A268" s="9">
         <v>43525</v>
       </c>
@@ -9153,7 +9156,7 @@
       <c r="L268" s="12"/>
       <c r="N268" s="21"/>
     </row>
-    <row r="269" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="269" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A269" s="9">
         <v>43556</v>
       </c>
@@ -9191,7 +9194,7 @@
       <c r="L269" s="12"/>
       <c r="N269" s="21"/>
     </row>
-    <row r="270" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="270" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A270" s="9">
         <v>43586</v>
       </c>
@@ -9229,7 +9232,7 @@
       <c r="L270" s="12"/>
       <c r="N270" s="21"/>
     </row>
-    <row r="271" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="271" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A271" s="9">
         <v>43617</v>
       </c>
@@ -9267,7 +9270,7 @@
       <c r="L271" s="12"/>
       <c r="N271" s="21"/>
     </row>
-    <row r="272" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="272" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A272" s="9">
         <v>43647</v>
       </c>
@@ -9305,7 +9308,7 @@
       <c r="L272" s="12"/>
       <c r="N272" s="21"/>
     </row>
-    <row r="273" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="273" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A273" s="9">
         <v>43678</v>
       </c>
@@ -9343,7 +9346,7 @@
       <c r="L273" s="12"/>
       <c r="N273" s="21"/>
     </row>
-    <row r="274" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="274" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A274" s="9">
         <v>43709</v>
       </c>
@@ -9381,7 +9384,7 @@
       <c r="L274" s="12"/>
       <c r="N274" s="21"/>
     </row>
-    <row r="275" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="275" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A275" s="9">
         <v>43739</v>
       </c>
@@ -9419,7 +9422,7 @@
       <c r="L275" s="12"/>
       <c r="N275" s="21"/>
     </row>
-    <row r="276" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="276" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A276" s="9">
         <v>43770</v>
       </c>
@@ -9457,7 +9460,7 @@
       <c r="L276" s="12"/>
       <c r="N276" s="21"/>
     </row>
-    <row r="277" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="277" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A277" s="9">
         <v>43800</v>
       </c>
@@ -9495,7 +9498,7 @@
       <c r="L277" s="12"/>
       <c r="N277" s="21"/>
     </row>
-    <row r="278" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="278" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A278" s="9">
         <v>43831</v>
       </c>
@@ -9533,7 +9536,7 @@
       <c r="L278" s="12"/>
       <c r="N278" s="21"/>
     </row>
-    <row r="279" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="279" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A279" s="9">
         <v>43862</v>
       </c>
@@ -9571,7 +9574,7 @@
       <c r="L279" s="12"/>
       <c r="N279" s="21"/>
     </row>
-    <row r="280" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="280" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A280" s="9">
         <v>43891</v>
       </c>
@@ -9609,7 +9612,7 @@
       <c r="L280" s="12"/>
       <c r="N280" s="21"/>
     </row>
-    <row r="281" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="281" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A281" s="9">
         <v>43922</v>
       </c>
@@ -9647,7 +9650,7 @@
       <c r="L281" s="12"/>
       <c r="N281" s="21"/>
     </row>
-    <row r="282" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="282" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A282" s="9">
         <v>43952</v>
       </c>
@@ -9685,7 +9688,7 @@
       <c r="L282" s="12"/>
       <c r="N282" s="21"/>
     </row>
-    <row r="283" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="283" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A283" s="9">
         <v>43983</v>
       </c>
@@ -9723,7 +9726,7 @@
       <c r="L283" s="12"/>
       <c r="N283" s="21"/>
     </row>
-    <row r="284" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="284" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A284" s="9">
         <v>44013</v>
       </c>
@@ -9761,7 +9764,7 @@
       <c r="L284" s="12"/>
       <c r="N284" s="21"/>
     </row>
-    <row r="285" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="285" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A285" s="9">
         <v>44044</v>
       </c>
@@ -9799,7 +9802,7 @@
       <c r="L285" s="12"/>
       <c r="N285" s="21"/>
     </row>
-    <row r="286" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="286" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A286" s="9">
         <v>44075</v>
       </c>
@@ -9837,7 +9840,7 @@
       <c r="L286" s="12"/>
       <c r="N286" s="21"/>
     </row>
-    <row r="287" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="287" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A287" s="9">
         <v>44105</v>
       </c>
@@ -9875,7 +9878,7 @@
       <c r="L287" s="12"/>
       <c r="N287" s="21"/>
     </row>
-    <row r="288" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="288" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A288" s="9">
         <v>44136</v>
       </c>
@@ -9913,7 +9916,7 @@
       <c r="L288" s="12"/>
       <c r="N288" s="21"/>
     </row>
-    <row r="289" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="289" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A289" s="9">
         <v>44166</v>
       </c>
@@ -9951,7 +9954,7 @@
       <c r="L289" s="12"/>
       <c r="N289" s="21"/>
     </row>
-    <row r="290" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="290" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A290" s="9">
         <v>44197</v>
       </c>
@@ -9989,7 +9992,7 @@
       <c r="L290" s="12"/>
       <c r="N290" s="21"/>
     </row>
-    <row r="291" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="291" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A291" s="9">
         <v>44228</v>
       </c>
@@ -10027,7 +10030,7 @@
       <c r="L291" s="12"/>
       <c r="N291" s="21"/>
     </row>
-    <row r="292" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="292" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A292" s="9">
         <v>44256</v>
       </c>
@@ -10065,7 +10068,7 @@
       <c r="L292" s="12"/>
       <c r="N292" s="21"/>
     </row>
-    <row r="293" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="293" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A293" s="9">
         <v>44287</v>
       </c>
@@ -10103,7 +10106,7 @@
       <c r="L293" s="12"/>
       <c r="N293" s="21"/>
     </row>
-    <row r="294" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="294" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A294" s="9">
         <v>44317</v>
       </c>
@@ -10141,7 +10144,7 @@
       <c r="L294" s="12"/>
       <c r="N294" s="21"/>
     </row>
-    <row r="295" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="295" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A295" s="9">
         <v>44348</v>
       </c>
@@ -10179,7 +10182,7 @@
       <c r="L295" s="12"/>
       <c r="N295" s="21"/>
     </row>
-    <row r="296" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="296" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A296" s="9">
         <v>44378</v>
       </c>
@@ -10217,7 +10220,7 @@
       <c r="L296" s="12"/>
       <c r="N296" s="21"/>
     </row>
-    <row r="297" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="297" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A297" s="9">
         <v>44409</v>
       </c>
@@ -10255,7 +10258,7 @@
       <c r="L297" s="12"/>
       <c r="N297" s="21"/>
     </row>
-    <row r="298" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="298" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A298" s="9">
         <v>44440</v>
       </c>
@@ -10293,7 +10296,7 @@
       <c r="L298" s="12"/>
       <c r="N298" s="21"/>
     </row>
-    <row r="299" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="299" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A299" s="9">
         <v>44470</v>
       </c>
@@ -10331,7 +10334,7 @@
       <c r="L299" s="12"/>
       <c r="N299" s="21"/>
     </row>
-    <row r="300" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="300" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A300" s="9">
         <v>44501</v>
       </c>
@@ -10369,7 +10372,7 @@
       <c r="L300" s="12"/>
       <c r="N300" s="21"/>
     </row>
-    <row r="301" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="301" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A301" s="9">
         <v>44531</v>
       </c>
@@ -10407,7 +10410,7 @@
       <c r="L301" s="12"/>
       <c r="N301" s="21"/>
     </row>
-    <row r="302" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="302" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A302" s="9">
         <v>44562</v>
       </c>
@@ -10445,7 +10448,7 @@
       <c r="L302" s="12"/>
       <c r="N302" s="21"/>
     </row>
-    <row r="303" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="303" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A303" s="9">
         <v>44593</v>
       </c>
@@ -10483,7 +10486,7 @@
       <c r="L303" s="12"/>
       <c r="N303" s="21"/>
     </row>
-    <row r="304" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="304" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A304" s="9">
         <v>44621</v>
       </c>
@@ -10521,7 +10524,7 @@
       <c r="L304" s="12"/>
       <c r="N304" s="21"/>
     </row>
-    <row r="305" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="305" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A305" s="9">
         <v>44652</v>
       </c>
@@ -10559,7 +10562,7 @@
       <c r="L305" s="12"/>
       <c r="N305" s="21"/>
     </row>
-    <row r="306" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="306" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A306" s="9">
         <v>44682</v>
       </c>
@@ -10597,7 +10600,7 @@
       <c r="L306" s="12"/>
       <c r="N306" s="21"/>
     </row>
-    <row r="307" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="307" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A307" s="9">
         <v>44713</v>
       </c>
@@ -10635,7 +10638,7 @@
       <c r="L307" s="12"/>
       <c r="N307" s="21"/>
     </row>
-    <row r="308" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="308" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A308" s="9">
         <v>44743</v>
       </c>
@@ -10673,7 +10676,7 @@
       <c r="L308" s="12"/>
       <c r="N308" s="21"/>
     </row>
-    <row r="309" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="309" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A309" s="9">
         <v>44774</v>
       </c>
@@ -10711,7 +10714,7 @@
       <c r="L309" s="12"/>
       <c r="N309" s="21"/>
     </row>
-    <row r="310" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="310" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A310" s="9">
         <v>44805</v>
       </c>
@@ -10749,7 +10752,7 @@
       <c r="L310" s="12"/>
       <c r="N310" s="21"/>
     </row>
-    <row r="311" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="311" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A311" s="9">
         <v>44835</v>
       </c>
@@ -10787,7 +10790,7 @@
       <c r="L311" s="12"/>
       <c r="N311" s="21"/>
     </row>
-    <row r="312" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="312" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A312" s="9">
         <v>44866</v>
       </c>
@@ -10825,7 +10828,7 @@
       <c r="L312" s="12"/>
       <c r="N312" s="21"/>
     </row>
-    <row r="313" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="313" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A313" s="9">
         <v>44896</v>
       </c>
@@ -10863,7 +10866,7 @@
       <c r="L313" s="12"/>
       <c r="N313" s="21"/>
     </row>
-    <row r="314" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="314" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A314" s="9">
         <v>44927</v>
       </c>
@@ -10901,7 +10904,7 @@
       <c r="L314" s="12"/>
       <c r="N314" s="21"/>
     </row>
-    <row r="315" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="315" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A315" s="9">
         <v>44958</v>
       </c>
@@ -10939,7 +10942,7 @@
       <c r="L315" s="12"/>
       <c r="N315" s="21"/>
     </row>
-    <row r="316" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="316" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A316" s="9">
         <v>44986</v>
       </c>
@@ -10977,7 +10980,7 @@
       <c r="L316" s="12"/>
       <c r="N316" s="21"/>
     </row>
-    <row r="317" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="317" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A317" s="9">
         <v>45017</v>
       </c>
@@ -11015,7 +11018,7 @@
       <c r="L317" s="12"/>
       <c r="N317" s="21"/>
     </row>
-    <row r="318" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="318" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A318" s="9">
         <v>45047</v>
       </c>
@@ -11053,7 +11056,7 @@
       <c r="L318" s="12"/>
       <c r="N318" s="21"/>
     </row>
-    <row r="319" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="319" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A319" s="9">
         <v>45078</v>
       </c>
@@ -11091,7 +11094,7 @@
       <c r="L319" s="12"/>
       <c r="N319" s="21"/>
     </row>
-    <row r="320" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="320" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A320" s="9">
         <v>45108</v>
       </c>
@@ -11129,7 +11132,7 @@
       <c r="L320" s="12"/>
       <c r="N320" s="21"/>
     </row>
-    <row r="321" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="321" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A321" s="9">
         <v>45139</v>
       </c>
@@ -11167,7 +11170,7 @@
       <c r="L321" s="12"/>
       <c r="N321" s="21"/>
     </row>
-    <row r="322" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="322" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A322" s="9">
         <v>45170</v>
       </c>
@@ -11205,7 +11208,7 @@
       <c r="L322" s="12"/>
       <c r="N322" s="21"/>
     </row>
-    <row r="323" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="323" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A323" s="9">
         <v>45200</v>
       </c>
@@ -11258,7 +11261,7 @@
       <c r="L323" s="12"/>
       <c r="N323" s="21"/>
     </row>
-    <row r="324" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="324" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A324" s="9">
         <v>45231</v>
       </c>
@@ -11296,7 +11299,7 @@
       <c r="L324" s="12"/>
       <c r="N324" s="21"/>
     </row>
-    <row r="325" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="325" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A325" s="9">
         <v>45261</v>
       </c>
@@ -11334,7 +11337,7 @@
       <c r="L325" s="12"/>
       <c r="N325" s="21"/>
     </row>
-    <row r="326" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="326" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A326" s="9">
         <v>45292</v>
       </c>
@@ -11372,7 +11375,7 @@
       <c r="L326" s="12"/>
       <c r="N326" s="21"/>
     </row>
-    <row r="327" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="327" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A327" s="9">
         <v>45323</v>
       </c>
@@ -11410,7 +11413,7 @@
       <c r="L327" s="12"/>
       <c r="N327" s="21"/>
     </row>
-    <row r="328" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="328" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A328" s="9">
         <v>45352</v>
       </c>
@@ -11448,7 +11451,7 @@
       <c r="L328" s="12"/>
       <c r="N328" s="21"/>
     </row>
-    <row r="329" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="329" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A329" s="9">
         <v>45383</v>
       </c>
@@ -11486,7 +11489,7 @@
       <c r="L329" s="12"/>
       <c r="N329" s="21"/>
     </row>
-    <row r="330" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="330" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A330" s="9">
         <v>45413</v>
       </c>
@@ -11524,7 +11527,7 @@
       <c r="L330" s="12"/>
       <c r="N330" s="21"/>
     </row>
-    <row r="331" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="331" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A331" s="9">
         <v>45444</v>
       </c>
@@ -11562,7 +11565,7 @@
       <c r="L331" s="12"/>
       <c r="N331" s="21"/>
     </row>
-    <row r="332" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="332" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A332" s="9">
         <v>45474</v>
       </c>
@@ -11600,7 +11603,7 @@
       <c r="L332" s="12"/>
       <c r="N332" s="21"/>
     </row>
-    <row r="333" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="333" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A333" s="16">
         <v>45505</v>
       </c>
@@ -11638,7 +11641,7 @@
       <c r="L333" s="17"/>
       <c r="N333" s="21"/>
     </row>
-    <row r="334" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="334" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A334" s="16">
         <v>45536</v>
       </c>
@@ -11676,7 +11679,7 @@
       <c r="L334" s="17"/>
       <c r="N334" s="21"/>
     </row>
-    <row r="335" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="335" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A335" s="9">
         <v>45566</v>
       </c>
@@ -11714,7 +11717,7 @@
       <c r="L335" s="17"/>
       <c r="N335" s="21"/>
     </row>
-    <row r="336" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="336" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A336" s="9">
         <v>45597</v>
       </c>
@@ -11752,7 +11755,7 @@
       <c r="L336" s="17"/>
       <c r="N336" s="21"/>
     </row>
-    <row r="337" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="337" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A337" s="9">
         <v>45627</v>
       </c>
@@ -11790,7 +11793,7 @@
       <c r="L337" s="17"/>
       <c r="N337" s="21"/>
     </row>
-    <row r="338" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="338" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A338" s="16">
         <v>45658</v>
       </c>
@@ -11828,7 +11831,7 @@
       <c r="L338" s="17"/>
       <c r="N338" s="21"/>
     </row>
-    <row r="339" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="339" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A339" s="16">
         <v>45689</v>
       </c>
@@ -11866,7 +11869,7 @@
       <c r="L339" s="17"/>
       <c r="N339" s="21"/>
     </row>
-    <row r="340" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="340" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A340" s="16">
         <v>45717</v>
       </c>
@@ -11904,7 +11907,7 @@
       <c r="L340" s="17"/>
       <c r="N340" s="21"/>
     </row>
-    <row r="341" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="341" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A341" s="16">
         <v>45748</v>
       </c>
@@ -11942,7 +11945,7 @@
       <c r="L341" s="17"/>
       <c r="N341" s="21"/>
     </row>
-    <row r="342" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="342" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A342" s="16">
         <v>45778</v>
       </c>
@@ -11980,7 +11983,7 @@
       <c r="L342" s="17"/>
       <c r="N342" s="21"/>
     </row>
-    <row r="343" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="343" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A343" s="16">
         <v>45809</v>
       </c>
@@ -12018,7 +12021,7 @@
       <c r="L343" s="17"/>
       <c r="N343" s="21"/>
     </row>
-    <row r="344" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="344" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A344" s="16">
         <v>45839</v>
       </c>
@@ -12056,7 +12059,7 @@
       <c r="L344" s="17"/>
       <c r="N344" s="21"/>
     </row>
-    <row r="345" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="345" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A345" s="16">
         <v>45870</v>
       </c>
@@ -12094,7 +12097,7 @@
       <c r="L345" s="17"/>
       <c r="N345" s="21"/>
     </row>
-    <row r="346" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="346" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A346" s="16">
         <v>45901</v>
       </c>
@@ -12132,7 +12135,7 @@
       <c r="L346" s="17"/>
       <c r="N346" s="21"/>
     </row>
-    <row r="347" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="347" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A347" s="16">
         <v>45931</v>
       </c>
@@ -12170,7 +12173,7 @@
       <c r="L347" s="17"/>
       <c r="N347" s="21"/>
     </row>
-    <row r="348" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="348" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A348" s="16">
         <v>45962</v>
       </c>
@@ -12208,7 +12211,7 @@
       <c r="L348" s="17"/>
       <c r="N348" s="21"/>
     </row>
-    <row r="349" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="349" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A349" s="16">
         <v>45992</v>
       </c>
@@ -12246,7 +12249,7 @@
       <c r="L349" s="17"/>
       <c r="N349" s="21"/>
     </row>
-    <row r="350" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="350" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A350" s="16">
         <v>46023</v>
       </c>
@@ -12284,7 +12287,7 @@
       <c r="L350" s="17"/>
       <c r="N350" s="21"/>
     </row>
-    <row r="351" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="351" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A351" s="16">
         <v>46054</v>
       </c>
@@ -12322,7 +12325,7 @@
       <c r="L351" s="17"/>
       <c r="N351" s="21"/>
     </row>
-    <row r="352" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="352" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A352" s="9">
         <v>46082</v>
       </c>
@@ -12359,7 +12362,7 @@
       </c>
       <c r="N352" s="21"/>
     </row>
-    <row r="353" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="353" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A353" s="9">
         <v>46113</v>
       </c>
@@ -12396,7 +12399,7 @@
       </c>
       <c r="N353" s="21"/>
     </row>
-    <row r="354" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="354" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A354" s="9">
         <v>46143</v>
       </c>
@@ -12433,25 +12436,25 @@
       </c>
       <c r="N354" s="21"/>
     </row>
-    <row r="355" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="355" spans="1:14" x14ac:dyDescent="0.2">
       <c r="N355" s="21"/>
     </row>
-    <row r="356" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="356" spans="1:14" x14ac:dyDescent="0.2">
       <c r="N356" s="21"/>
     </row>
-    <row r="357" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="357" spans="1:14" x14ac:dyDescent="0.2">
       <c r="N357" s="21"/>
     </row>
-    <row r="358" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="358" spans="1:14" x14ac:dyDescent="0.2">
       <c r="N358" s="21"/>
     </row>
-    <row r="359" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="359" spans="1:14" x14ac:dyDescent="0.2">
       <c r="N359" s="21"/>
     </row>
-    <row r="360" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="360" spans="1:14" x14ac:dyDescent="0.2">
       <c r="N360" s="21"/>
     </row>
-    <row r="361" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="361" spans="1:14" x14ac:dyDescent="0.2">
       <c r="N361" s="21"/>
     </row>
   </sheetData>
@@ -12463,25 +12466,25 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D15FD8D4-D554-4318-A394-AC69A9CC97B1}">
   <dimension ref="B2:C3"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="2" max="2" width="9.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B2" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="20" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B3" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="20" t="s">
+      <c r="C3" t="s">
         <v>3</v>
-      </c>
-    </row>
-    <row r="3" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B3" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="C3" t="s">
-        <v>5</v>
       </c>
     </row>
   </sheetData>
@@ -12493,27 +12496,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <Description xmlns="0bd4d3c9-04aa-442a-9f03-e370d3888c8a" xsi:nil="true"/>
-    <TaxCatchAll xmlns="6bdde3b2-7d08-4106-9f53-5b5c490aab7c" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="0bd4d3c9-04aa-442a-9f03-e370d3888c8a">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100BA02CEE7E06592488AB9FB206B163FCE" ma:contentTypeVersion="19" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="d93301254c9a61fd9ec1c786889d2043">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="0bd4d3c9-04aa-442a-9f03-e370d3888c8a" xmlns:ns3="6bdde3b2-7d08-4106-9f53-5b5c490aab7c" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="3b4d0496092f7727c4ca0d2dd8128c72" ns2:_="" ns3:_="">
     <xsd:import namespace="0bd4d3c9-04aa-442a-9f03-e370d3888c8a"/>
@@ -12776,10 +12758,42 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <Description xmlns="0bd4d3c9-04aa-442a-9f03-e370d3888c8a" xsi:nil="true"/>
+    <TaxCatchAll xmlns="6bdde3b2-7d08-4106-9f53-5b5c490aab7c" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="0bd4d3c9-04aa-442a-9f03-e370d3888c8a">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BE9CA77C-FCD5-4033-B7FF-8909DEC82D18}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A053C9B4-F58E-49F8-9C05-2F9558B34822}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="0bd4d3c9-04aa-442a-9f03-e370d3888c8a"/>
+    <ds:schemaRef ds:uri="6bdde3b2-7d08-4106-9f53-5b5c490aab7c"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -12802,20 +12816,9 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A053C9B4-F58E-49F8-9C05-2F9558B34822}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BE9CA77C-FCD5-4033-B7FF-8909DEC82D18}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="0bd4d3c9-04aa-442a-9f03-e370d3888c8a"/>
-    <ds:schemaRef ds:uri="6bdde3b2-7d08-4106-9f53-5b5c490aab7c"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>